--- a/exports/trend_1d/BOSCHLTD_full_report.xlsx
+++ b/exports/trend_1d/BOSCHLTD_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>7.8</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="H2" t="n">
-        <v>23039.9</v>
+        <v>22358.7</v>
       </c>
       <c r="I2" t="n">
         <v>22869.45562440789</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>7.99</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.85</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>13.12</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42046</v>
+        <v>42047</v>
       </c>
       <c r="H3" t="n">
-        <v>23708.1</v>
+        <v>25361.3</v>
       </c>
       <c r="I3" t="n">
         <v>25293.21321482598</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.04</v>
+        <v>-13.43</v>
       </c>
       <c r="L3" t="n">
-        <v>7.13</v>
+        <v>15.68</v>
       </c>
       <c r="M3" t="n">
-        <v>0.54</v>
+        <v>3.44</v>
       </c>
       <c r="N3" t="n">
-        <v>3.01</v>
+        <v>6.97</v>
       </c>
       <c r="O3" t="n">
         <v>-2.96</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>12.73</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42111</v>
+        <v>42114</v>
       </c>
       <c r="H4" t="n">
-        <v>25574.55</v>
+        <v>24676.2</v>
       </c>
       <c r="I4" t="n">
         <v>25176.64800043231</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K4" t="n">
-        <v>0.84</v>
+        <v>-2.7</v>
       </c>
       <c r="L4" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="M4" t="n">
         <v>2.63</v>
       </c>
       <c r="N4" t="n">
-        <v>3.38</v>
+        <v>3.51</v>
       </c>
       <c r="O4" t="n">
         <v>6.97</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.9</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42186</v>
+        <v>42187</v>
       </c>
       <c r="H5" t="n">
-        <v>22039.35</v>
+        <v>23014.85</v>
       </c>
       <c r="I5" t="n">
         <v>22449.71915562821</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K5" t="n">
-        <v>10.69</v>
+        <v>6.73</v>
       </c>
       <c r="L5" t="n">
         <v>4.49</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.39</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42236</v>
+        <v>42237</v>
       </c>
       <c r="H6" t="n">
-        <v>24820.85</v>
+        <v>24122.15</v>
       </c>
       <c r="I6" t="n">
         <v>24299.03582040351</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K6" t="n">
-        <v>7.85</v>
+        <v>4.81</v>
       </c>
       <c r="L6" t="n">
         <v>4.8</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.83</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42297</v>
+        <v>42298</v>
       </c>
       <c r="H7" t="n">
-        <v>21562.6</v>
+        <v>21743.2</v>
       </c>
       <c r="I7" t="n">
         <v>21650.18471783378</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K7" t="n">
-        <v>10.61</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>2.23</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.33</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42311</v>
+        <v>42312</v>
       </c>
       <c r="H8" t="n">
-        <v>20700.09</v>
+        <v>20264.15</v>
       </c>
       <c r="I8" t="n">
         <v>20326.80596360159</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.8</v>
+        <v>-6.8</v>
       </c>
       <c r="L8" t="n">
         <v>7.48</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42437</v>
+        <v>42438</v>
       </c>
       <c r="H9" t="n">
-        <v>17441.25</v>
+        <v>17932.95</v>
       </c>
       <c r="I9" t="n">
         <v>17682.15826218752</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K9" t="n">
-        <v>13.93</v>
+        <v>11.5</v>
       </c>
       <c r="L9" t="n">
         <v>2.84</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.99</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42466</v>
+        <v>42467</v>
       </c>
       <c r="H10" t="n">
-        <v>19237.95</v>
+        <v>18916.15</v>
       </c>
       <c r="I10" t="n">
         <v>19045.84463208235</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K10" t="n">
-        <v>7.28</v>
+        <v>5.48</v>
       </c>
       <c r="L10" t="n">
         <v>4.09</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.95</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42501</v>
+        <v>42502</v>
       </c>
       <c r="H11" t="n">
-        <v>20046.1</v>
+        <v>20925.25</v>
       </c>
       <c r="I11" t="n">
         <v>20474.91028190842</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.97</v>
+        <v>-10.62</v>
       </c>
       <c r="L11" t="n">
-        <v>7.84</v>
+        <v>11.17</v>
       </c>
       <c r="M11" t="n">
         <v>1.14</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.44</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42604</v>
+        <v>42605</v>
       </c>
       <c r="H12" t="n">
-        <v>23695.55</v>
+        <v>23598.45</v>
       </c>
       <c r="I12" t="n">
         <v>23692.41827247827</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K12" t="n">
-        <v>13.24</v>
+        <v>12.77</v>
       </c>
       <c r="L12" t="n">
         <v>4.68</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>7.07</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42706</v>
+        <v>42709</v>
       </c>
       <c r="H13" t="n">
-        <v>20361.65</v>
+        <v>20850.8</v>
       </c>
       <c r="I13" t="n">
         <v>20700.65924508351</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K13" t="n">
-        <v>13.72</v>
+        <v>11.64</v>
       </c>
       <c r="L13" t="n">
         <v>5.28</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.97</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H14" t="n">
-        <v>23141.6</v>
+        <v>22825.9</v>
       </c>
       <c r="I14" t="n">
         <v>22908.75354440869</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K14" t="n">
-        <v>10.99</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="L14" t="n">
         <v>9</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42948</v>
+        <v>42949</v>
       </c>
       <c r="H15" t="n">
-        <v>24666.5</v>
+        <v>25029.75</v>
       </c>
       <c r="I15" t="n">
         <v>24739.14324830965</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.06</v>
+        <v>-9.66</v>
       </c>
       <c r="L15" t="n">
         <v>10.58</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>6.39</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42957</v>
+        <v>42958</v>
       </c>
       <c r="H16" t="n">
-        <v>23543.8</v>
+        <v>22623.2</v>
       </c>
       <c r="I16" t="n">
         <v>23431.50311391578</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.94</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>6.82</v>
+        <v>11.07</v>
       </c>
       <c r="M16" t="n">
-        <v>0.55</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>2.03</v>
+        <v>3.91</v>
       </c>
       <c r="O16" t="n">
         <v>1.47</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43021</v>
+        <v>43024</v>
       </c>
       <c r="H17" t="n">
-        <v>21571.6</v>
+        <v>22199.3</v>
       </c>
       <c r="I17" t="n">
         <v>22057.20243110518</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K17" t="n">
-        <v>4.65</v>
+        <v>1.87</v>
       </c>
       <c r="L17" t="n">
         <v>4.37</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>7.41</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43048</v>
+        <v>43049</v>
       </c>
       <c r="H18" t="n">
-        <v>21126.2</v>
+        <v>20457.05</v>
       </c>
       <c r="I18" t="n">
         <v>20712.10378919624</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.83</v>
+        <v>-7.85</v>
       </c>
       <c r="L18" t="n">
-        <v>7.6</v>
+        <v>8.76</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9</v>
+        <v>1.21</v>
       </c>
       <c r="N18" t="n">
-        <v>2.07</v>
+        <v>3.17</v>
       </c>
       <c r="O18" t="n">
         <v>2.91</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.87</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43068</v>
+        <v>43069</v>
       </c>
       <c r="H19" t="n">
-        <v>20065.65</v>
+        <v>20333.75</v>
       </c>
       <c r="I19" t="n">
         <v>20094.15699401751</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>1.91</v>
+        <v>0.6</v>
       </c>
       <c r="L19" t="n">
         <v>3.53</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>7.22</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43152</v>
+        <v>43153</v>
       </c>
       <c r="H20" t="n">
-        <v>19160.05</v>
+        <v>18889.7</v>
       </c>
       <c r="I20" t="n">
         <v>19047.39320070405</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.77</v>
+        <v>-7.1</v>
       </c>
       <c r="L20" t="n">
-        <v>6.13</v>
+        <v>8.59</v>
       </c>
       <c r="M20" t="n">
         <v>2.26</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>5.5</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43187</v>
+        <v>43192</v>
       </c>
       <c r="H21" t="n">
-        <v>18017.55</v>
+        <v>18515</v>
       </c>
       <c r="I21" t="n">
         <v>18448.93736846558</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K21" t="n">
-        <v>4.62</v>
+        <v>1.98</v>
       </c>
       <c r="L21" t="n">
         <v>2.17</v>
       </c>
       <c r="M21" t="n">
-        <v>0.71</v>
+        <v>1.57</v>
       </c>
       <c r="N21" t="n">
-        <v>2.29</v>
+        <v>2.76</v>
       </c>
       <c r="O21" t="n">
         <v>-1.41</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43231</v>
+        <v>43234</v>
       </c>
       <c r="H22" t="n">
-        <v>18658</v>
+        <v>18212.8</v>
       </c>
       <c r="I22" t="n">
         <v>18427.26541886707</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K22" t="n">
-        <v>0.77</v>
+        <v>-1.63</v>
       </c>
       <c r="L22" t="n">
         <v>3.98</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>8.31</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43256</v>
+        <v>43257</v>
       </c>
       <c r="H23" t="n">
-        <v>17912.45</v>
+        <v>18958.7</v>
       </c>
       <c r="I23" t="n">
         <v>18886.99850096237</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K23" t="n">
-        <v>1.65</v>
+        <v>-4.1</v>
       </c>
       <c r="L23" t="n">
-        <v>3.22</v>
+        <v>4.87</v>
       </c>
       <c r="M23" t="n">
         <v>0.87</v>
       </c>
       <c r="N23" t="n">
-        <v>3.35</v>
+        <v>5.84</v>
       </c>
       <c r="O23" t="n">
         <v>-2.39</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>11.35</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H24" t="n">
-        <v>20622.8</v>
+        <v>19998.4</v>
       </c>
       <c r="I24" t="n">
         <v>20058.61645119651</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K24" t="n">
-        <v>8.779999999999999</v>
+        <v>5.48</v>
       </c>
       <c r="L24" t="n">
         <v>9.529999999999999</v>
@@ -1809,7 +2096,7 @@
         <v>1.14</v>
       </c>
       <c r="N24" t="n">
-        <v>2.77</v>
+        <v>3.03</v>
       </c>
       <c r="O24" t="n">
         <v>5.84</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.89</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43496</v>
+        <v>43497</v>
       </c>
       <c r="H25" t="n">
-        <v>18851.7</v>
+        <v>19316.15</v>
       </c>
       <c r="I25" t="n">
         <v>19291.71931209692</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K25" t="n">
-        <v>5.73</v>
+        <v>3.41</v>
       </c>
       <c r="L25" t="n">
         <v>4</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>8.01</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43508</v>
+        <v>43509</v>
       </c>
       <c r="H26" t="n">
-        <v>18592.2</v>
+        <v>17908.45</v>
       </c>
       <c r="I26" t="n">
         <v>18070.10490091141</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.75</v>
+        <v>-7.29</v>
       </c>
       <c r="L26" t="n">
-        <v>4.22</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>0.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.58</v>
+        <v>3.68</v>
       </c>
       <c r="O26" t="n">
         <v>2.46</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43765</v>
+        <v>43767</v>
       </c>
       <c r="H27" t="n">
-        <v>14685</v>
+        <v>15654.8</v>
       </c>
       <c r="I27" t="n">
         <v>14751.72505770801</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K27" t="n">
-        <v>18</v>
+        <v>12.58</v>
       </c>
       <c r="L27" t="n">
         <v>8.449999999999999</v>
@@ -1980,7 +2303,7 @@
         <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>5.42</v>
+        <v>6.6</v>
       </c>
       <c r="O27" t="n">
         <v>-3.68</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>170</v>
+        <v>171</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>9</v>
+      </c>
+      <c r="U27" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>12.7</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43808</v>
+        <v>43809</v>
       </c>
       <c r="H28" t="n">
-        <v>15218.4</v>
+        <v>14969.25</v>
       </c>
       <c r="I28" t="n">
         <v>15084.69918512976</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.79</v>
+        <v>-4.38</v>
       </c>
       <c r="L28" t="n">
         <v>6.8</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>11.05</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H29" t="n">
-        <v>10309.25</v>
+        <v>10499.3</v>
       </c>
       <c r="I29" t="n">
         <v>10476.90064053427</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K29" t="n">
-        <v>31.13</v>
+        <v>29.86</v>
       </c>
       <c r="L29" t="n">
         <v>5.68</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>7</v>
+      </c>
+      <c r="U29" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>12.33</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H30" t="n">
-        <v>14007.65</v>
+        <v>12814</v>
       </c>
       <c r="I30" t="n">
         <v>12854.43972175084</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K30" t="n">
-        <v>33.42</v>
+        <v>22.05</v>
       </c>
       <c r="L30" t="n">
         <v>2.85</v>
@@ -2151,7 +2510,7 @@
         <v>5.41</v>
       </c>
       <c r="N30" t="n">
-        <v>4.81</v>
+        <v>8.52</v>
       </c>
       <c r="O30" t="n">
         <v>1.84</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>18.25</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44158</v>
+        <v>44159</v>
       </c>
       <c r="H31" t="n">
-        <v>11819.5</v>
+        <v>12980</v>
       </c>
       <c r="I31" t="n">
         <v>12681.62696440893</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K31" t="n">
-        <v>7.76</v>
+        <v>-1.3</v>
       </c>
       <c r="L31" t="n">
         <v>10.93</v>
@@ -2208,7 +2579,7 @@
         <v>2.23</v>
       </c>
       <c r="N31" t="n">
-        <v>4.53</v>
+        <v>9.82</v>
       </c>
       <c r="O31" t="n">
         <v>-8.52</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>14.8</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44271</v>
+        <v>44272</v>
       </c>
       <c r="H32" t="n">
-        <v>14818.5</v>
+        <v>14623.85</v>
       </c>
       <c r="I32" t="n">
         <v>14730.22453952076</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K32" t="n">
-        <v>14.16</v>
+        <v>12.66</v>
       </c>
       <c r="L32" t="n">
         <v>9.09</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44333</v>
+        <v>44334</v>
       </c>
       <c r="H33" t="n">
-        <v>14218.85</v>
+        <v>14450.55</v>
       </c>
       <c r="I33" t="n">
         <v>14373.70784497092</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K33" t="n">
-        <v>2.77</v>
+        <v>1.19</v>
       </c>
       <c r="L33" t="n">
         <v>2.53</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44414</v>
+        <v>44417</v>
       </c>
       <c r="H34" t="n">
-        <v>14901.3</v>
+        <v>14711</v>
       </c>
       <c r="I34" t="n">
         <v>14750.81853416737</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K34" t="n">
-        <v>3.12</v>
+        <v>1.8</v>
       </c>
       <c r="L34" t="n">
         <v>2.31</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44454</v>
+        <v>44455</v>
       </c>
       <c r="H35" t="n">
-        <v>14580.2</v>
+        <v>15279.6</v>
       </c>
       <c r="I35" t="n">
         <v>14607.82162200016</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K35" t="n">
-        <v>0.89</v>
+        <v>-3.87</v>
       </c>
       <c r="L35" t="n">
-        <v>1.96</v>
+        <v>6.04</v>
       </c>
       <c r="M35" t="n">
         <v>0.63</v>
       </c>
       <c r="N35" t="n">
-        <v>1.71</v>
+        <v>4.8</v>
       </c>
       <c r="O35" t="n">
         <v>-1.28</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.47</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H36" t="n">
-        <v>17779.65</v>
+        <v>16934.45</v>
       </c>
       <c r="I36" t="n">
         <v>17089.44508300841</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K36" t="n">
-        <v>16.36</v>
+        <v>10.83</v>
       </c>
       <c r="L36" t="n">
         <v>4.05</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>15.48</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44560</v>
+        <v>44561</v>
       </c>
       <c r="H37" t="n">
-        <v>16872.15</v>
+        <v>17320.25</v>
       </c>
       <c r="I37" t="n">
         <v>17172.43533793286</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K37" t="n">
-        <v>0.37</v>
+        <v>-2.28</v>
       </c>
       <c r="L37" t="n">
         <v>6.15</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>10.24</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H38" t="n">
-        <v>16817.7</v>
+        <v>16470.75</v>
       </c>
       <c r="I38" t="n">
         <v>16549.80883710999</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.9</v>
+        <v>-4.9</v>
       </c>
       <c r="L38" t="n">
-        <v>4.09</v>
+        <v>5.72</v>
       </c>
       <c r="M38" t="n">
-        <v>0.27</v>
+        <v>1.8</v>
       </c>
       <c r="N38" t="n">
         <v>2.84</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44708</v>
+        <v>44711</v>
       </c>
       <c r="H39" t="n">
-        <v>14185.75</v>
+        <v>14436.75</v>
       </c>
       <c r="I39" t="n">
         <v>14281.39773007671</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K39" t="n">
-        <v>13.87</v>
+        <v>12.35</v>
       </c>
       <c r="L39" t="n">
         <v>3.38</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>10.14</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44728</v>
+        <v>44729</v>
       </c>
       <c r="H40" t="n">
-        <v>13550.5</v>
+        <v>13329.75</v>
       </c>
       <c r="I40" t="n">
         <v>13367.16266740982</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.14</v>
+        <v>-7.67</v>
       </c>
       <c r="L40" t="n">
-        <v>6.49</v>
+        <v>7.94</v>
       </c>
       <c r="M40" t="n">
         <v>0.96</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>9.67</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44736</v>
+        <v>44739</v>
       </c>
       <c r="H41" t="n">
-        <v>14266.8</v>
+        <v>14593.15</v>
       </c>
       <c r="I41" t="n">
         <v>14414.28464666105</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.03</v>
+        <v>-9.48</v>
       </c>
       <c r="L41" t="n">
-        <v>7.49</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="N41" t="n">
         <v>3.22</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H42" t="n">
-        <v>16592.6</v>
+        <v>16223.35</v>
       </c>
       <c r="I42" t="n">
         <v>16508.54823293077</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K42" t="n">
-        <v>13.7</v>
+        <v>11.17</v>
       </c>
       <c r="L42" t="n">
         <v>1.83</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.56</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44862</v>
+        <v>44865</v>
       </c>
       <c r="H43" t="n">
-        <v>16114.4</v>
+        <v>16488.6</v>
       </c>
       <c r="I43" t="n">
         <v>16484.39929779334</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K43" t="n">
-        <v>0.67</v>
+        <v>-1.63</v>
       </c>
       <c r="L43" t="n">
         <v>3.77</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.61</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44950</v>
+        <v>44951</v>
       </c>
       <c r="H44" t="n">
-        <v>17049.5</v>
+        <v>16720.35</v>
       </c>
       <c r="I44" t="n">
         <v>16748.3256247781</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K44" t="n">
-        <v>3.4</v>
+        <v>1.41</v>
       </c>
       <c r="L44" t="n">
         <v>2.3</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>6.03</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44971</v>
+        <v>44972</v>
       </c>
       <c r="H45" t="n">
-        <v>17412.4</v>
+        <v>17855.25</v>
       </c>
       <c r="I45" t="n">
         <v>17580.10656092579</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.14</v>
+        <v>-6.79</v>
       </c>
       <c r="L45" t="n">
-        <v>5.66</v>
+        <v>7.95</v>
       </c>
       <c r="M45" t="n">
         <v>0.95</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.95</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45072</v>
+        <v>45075</v>
       </c>
       <c r="H46" t="n">
-        <v>18941.7</v>
+        <v>18296</v>
       </c>
       <c r="I46" t="n">
         <v>18629.3525925458</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K46" t="n">
-        <v>6.08</v>
+        <v>2.47</v>
       </c>
       <c r="L46" t="n">
         <v>3.47</v>
@@ -3063,7 +3614,7 @@
         <v>0.8</v>
       </c>
       <c r="N46" t="n">
-        <v>2.74</v>
+        <v>3.41</v>
       </c>
       <c r="O46" t="n">
         <v>2.54</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>7.85</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45113</v>
+        <v>45114</v>
       </c>
       <c r="H47" t="n">
-        <v>19514.85</v>
+        <v>19740.75</v>
       </c>
       <c r="I47" t="n">
         <v>19556.69399463071</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.66</v>
+        <v>-7.9</v>
       </c>
       <c r="L47" t="n">
-        <v>7.12</v>
+        <v>9.26</v>
       </c>
       <c r="M47" t="n">
         <v>0.6899999999999999</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>5.4</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45139</v>
+        <v>45140</v>
       </c>
       <c r="H48" t="n">
-        <v>18995.85</v>
+        <v>18262.25</v>
       </c>
       <c r="I48" t="n">
         <v>18673.93195144497</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.77</v>
+        <v>-7.49</v>
       </c>
       <c r="L48" t="n">
-        <v>5.07</v>
+        <v>8.27</v>
       </c>
       <c r="M48" t="n">
         <v>0.57</v>
       </c>
       <c r="N48" t="n">
-        <v>2.56</v>
+        <v>3.86</v>
       </c>
       <c r="O48" t="n">
         <v>1.16</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>7.97</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45169</v>
+        <v>45170</v>
       </c>
       <c r="H49" t="n">
-        <v>18573.85</v>
+        <v>18986.8</v>
       </c>
       <c r="I49" t="n">
         <v>18981.33254865101</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.71</v>
+        <v>-3.97</v>
       </c>
       <c r="L49" t="n">
-        <v>4.04</v>
+        <v>4.31</v>
       </c>
       <c r="M49" t="n">
         <v>0.82</v>
       </c>
       <c r="N49" t="n">
-        <v>1.38</v>
+        <v>2.22</v>
       </c>
       <c r="O49" t="n">
         <v>-3.86</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.32</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45198</v>
+        <v>45202</v>
       </c>
       <c r="H50" t="n">
-        <v>19019.7</v>
+        <v>18762.85</v>
       </c>
       <c r="I50" t="n">
         <v>18771.71261345222</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K50" t="n">
-        <v>0.17</v>
+        <v>-1.18</v>
       </c>
       <c r="L50" t="n">
         <v>2.53</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>6.22</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45210</v>
+        <v>45211</v>
       </c>
       <c r="H51" t="n">
-        <v>19698.1</v>
+        <v>20455.7</v>
       </c>
       <c r="I51" t="n">
         <v>19817.97872769428</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.98</v>
+        <v>-9.02</v>
       </c>
       <c r="L51" t="n">
-        <v>6.33</v>
+        <v>9.6</v>
       </c>
       <c r="M51" t="n">
         <v>0.21</v>
       </c>
       <c r="N51" t="n">
-        <v>2.39</v>
+        <v>3.85</v>
       </c>
       <c r="O51" t="n">
         <v>-1.35</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="H52" t="n">
-        <v>29787</v>
+        <v>29142.05</v>
       </c>
       <c r="I52" t="n">
         <v>29189.27401702309</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K52" t="n">
-        <v>45.62</v>
+        <v>42.46</v>
       </c>
       <c r="L52" t="n">
         <v>5.65</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>7</v>
+      </c>
+      <c r="U52" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>8.77</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="H53" t="n">
-        <v>30797.8</v>
+        <v>31882</v>
       </c>
       <c r="I53" t="n">
         <v>30929.09737670424</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.68</v>
+        <v>-9.4</v>
       </c>
       <c r="L53" t="n">
-        <v>6.48</v>
+        <v>10.15</v>
       </c>
       <c r="M53" t="n">
         <v>1.07</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>11.07</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H54" t="n">
-        <v>33909.75</v>
+        <v>32355.2</v>
       </c>
       <c r="I54" t="n">
         <v>32700.54742455174</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K54" t="n">
-        <v>6.36</v>
+        <v>1.48</v>
       </c>
       <c r="L54" t="n">
         <v>13.74</v>
       </c>
       <c r="M54" t="n">
-        <v>0.78</v>
+        <v>1.21</v>
       </c>
       <c r="N54" t="n">
-        <v>3.06</v>
+        <v>4.58</v>
       </c>
       <c r="O54" t="n">
         <v>3.52</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H55" t="n">
-        <v>33209.6</v>
+        <v>34113.9</v>
       </c>
       <c r="I55" t="n">
         <v>33818.2416817169</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.64</v>
+        <v>-5.44</v>
       </c>
       <c r="L55" t="n">
-        <v>5.53</v>
+        <v>5.95</v>
       </c>
       <c r="M55" t="n">
         <v>1.46</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.82</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45589</v>
+        <v>45590</v>
       </c>
       <c r="H56" t="n">
-        <v>36049.1</v>
+        <v>35931.95</v>
       </c>
       <c r="I56" t="n">
         <v>35937.41702663612</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K56" t="n">
-        <v>5.67</v>
+        <v>5.33</v>
       </c>
       <c r="L56" t="n">
         <v>1.98</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H57" t="n">
-        <v>27432.25</v>
+        <v>28276.8</v>
       </c>
       <c r="I57" t="n">
         <v>28248.86249246201</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K57" t="n">
-        <v>23.65</v>
+        <v>21.3</v>
       </c>
       <c r="L57" t="n">
         <v>2.97</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>6</v>
+      </c>
+      <c r="U57" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.85</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="H58" t="n">
-        <v>26516.3</v>
+        <v>26182.7</v>
       </c>
       <c r="I58" t="n">
         <v>26295.21266360069</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K58" t="n">
-        <v>-6.23</v>
+        <v>-7.41</v>
       </c>
       <c r="L58" t="n">
         <v>8.33</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>8.82</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45775</v>
+        <v>45776</v>
       </c>
       <c r="H59" t="n">
-        <v>28315</v>
+        <v>29165</v>
       </c>
       <c r="I59" t="n">
         <v>28492.56845806405</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.140000000000001</v>
+        <v>-11.39</v>
       </c>
       <c r="L59" t="n">
-        <v>9.33</v>
+        <v>11.71</v>
       </c>
       <c r="M59" t="n">
         <v>2.77</v>
       </c>
       <c r="N59" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="O59" t="n">
         <v>-1.26</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="H60" t="n">
-        <v>39390</v>
+        <v>38760</v>
       </c>
       <c r="I60" t="n">
         <v>38914.57350501301</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K60" t="n">
-        <v>35.06</v>
+        <v>32.9</v>
       </c>
       <c r="L60" t="n">
         <v>2.64</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>6.8</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="H61" t="n">
-        <v>36140</v>
+        <v>39420</v>
       </c>
       <c r="I61" t="n">
         <v>37156.64644149618</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K61" t="n">
-        <v>6.76</v>
+        <v>-1.7</v>
       </c>
       <c r="L61" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="M61" t="n">
         <v>0.75</v>
       </c>
       <c r="N61" t="n">
-        <v>2.23</v>
+        <v>9.08</v>
       </c>
       <c r="O61" t="n">
         <v>-1.6</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>5</v>
+      </c>
+      <c r="U61" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>10.69</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46038</v>
+        <v>46041</v>
       </c>
       <c r="H62" t="n">
-        <v>36835</v>
+        <v>36510</v>
       </c>
       <c r="I62" t="n">
         <v>36514.75676973435</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K62" t="n">
-        <v>-6.56</v>
+        <v>-7.38</v>
       </c>
       <c r="L62" t="n">
         <v>8.300000000000001</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>7.75</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H63" t="n">
-        <v>30635</v>
+        <v>32135</v>
       </c>
       <c r="I63" t="n">
         <v>31895.29658384466</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K63" t="n">
-        <v>16.09</v>
+        <v>11.98</v>
       </c>
       <c r="L63" t="n">
         <v>5.78</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>14.61</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="H64" t="n">
-        <v>47020</v>
+        <v>45700</v>
       </c>
       <c r="I64" t="n">
         <v>46082.98750533049</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K64" t="n">
-        <v>46.32</v>
+        <v>42.21</v>
       </c>
       <c r="L64" t="n">
         <v>6.96</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>6</v>
+      </c>
+      <c r="U64" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>9.01</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="H65" t="n">
-        <v>45600</v>
+        <v>47375</v>
       </c>
       <c r="I65" t="n">
         <v>46721.68994582578</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K65" t="n">
-        <v>0.22</v>
+        <v>-3.67</v>
       </c>
       <c r="L65" t="n">
         <v>4.04</v>
@@ -4146,7 +4925,7 @@
         <v>0.65</v>
       </c>
       <c r="N65" t="n">
-        <v>3.06</v>
+        <v>3.89</v>
       </c>
       <c r="O65" t="n">
         <v>-2.81</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4206,6 +4997,12 @@
       <c r="Q66" t="n">
         <v>1</v>
       </c>
+      <c r="R66" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9164,7 +9961,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.59999999999999</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="6">
@@ -9174,7 +9971,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="7">
@@ -9184,7 +9981,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8">
@@ -9194,7 +9991,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -9204,7 +10001,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="10">
@@ -9214,7 +10011,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>142.5</v>
+        <v>143.5</v>
       </c>
     </row>
     <row r="11">
@@ -9224,7 +10021,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -9234,7 +10031,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -9244,7 +10041,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.4</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="14">
@@ -9254,7 +10051,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.66</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="15">
@@ -9264,7 +10061,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.3</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="16">
@@ -9274,7 +10071,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.02</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="17">
@@ -9284,7 +10081,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>46.32</v>
+        <v>42.46</v>
       </c>
     </row>
     <row r="18">
@@ -9294,7 +10091,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>65.59999999999999</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -9304,7 +10101,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.3</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="20">
@@ -9314,7 +10111,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.74</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="21">
@@ -9324,7 +10121,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.74</v>
+        <v>15.68</v>
       </c>
     </row>
     <row r="22">
@@ -9334,7 +10131,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -9344,7 +10141,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -9354,7 +10151,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="25">
@@ -9374,7 +10171,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.66</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="27">
@@ -9394,7 +10191,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
